--- a/public/demo/results.xlsx
+++ b/public/demo/results.xlsx
@@ -18,10 +18,30 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CLO1 mark (%)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CLO2 mark (%)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CLO3 mark (%)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CLO4 mark (%)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>CLO5 mark (%)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -30,361 +50,843 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A19001</t>
+          <t>A26001</t>
         </is>
       </c>
       <c r="B2">
-        <v>62</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="C2">
+        <v>60</v>
+      </c>
+      <c r="D2">
+        <v>49</v>
+      </c>
+      <c r="E2">
+        <v>44</v>
+      </c>
+      <c r="F2">
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A19004</t>
+          <t>A26009</t>
         </is>
       </c>
       <c r="B3">
-        <v>71</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>late submission</t>
-        </is>
+        <v>84</v>
+      </c>
+      <c r="C3">
+        <v>87</v>
+      </c>
+      <c r="D3">
+        <v>87</v>
+      </c>
+      <c r="E3">
+        <v>87</v>
+      </c>
+      <c r="F3">
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A19011</t>
+          <t>A26017</t>
         </is>
       </c>
       <c r="B4">
-        <v>55</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>81</v>
+      </c>
+      <c r="D4">
+        <v>71</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+      <c r="F4">
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A19013</t>
+          <t>A26022</t>
         </is>
       </c>
       <c r="B5">
-        <v>68</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>41</v>
+      </c>
+      <c r="E5">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A19017</t>
+          <t>A26030</t>
         </is>
       </c>
       <c r="B6">
-        <v>47</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>resit</t>
-        </is>
+        <v>61</v>
+      </c>
+      <c r="C6">
+        <v>70</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6">
+        <v>45</v>
+      </c>
+      <c r="F6">
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A19020</t>
+          <t>A26038</t>
         </is>
       </c>
       <c r="B7">
-        <v>74</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>79</v>
+      </c>
+      <c r="C7">
+        <v>80</v>
+      </c>
+      <c r="D7">
+        <v>73</v>
+      </c>
+      <c r="E7">
+        <v>73</v>
+      </c>
+      <c r="F7">
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A19022</t>
+          <t>A26043</t>
         </is>
       </c>
       <c r="B8">
-        <v>59</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t/>
+        <v>55</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>medical leave</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A19025</t>
+          <t>A26051</t>
         </is>
       </c>
       <c r="B9">
-        <v>66</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="C9">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A19031</t>
+          <t>A26059</t>
         </is>
       </c>
       <c r="B10">
-        <v>52</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>73</v>
+      </c>
+      <c r="C10">
+        <v>74</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A19034</t>
+          <t>A26064</t>
         </is>
       </c>
       <c r="B11">
-        <v>70</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="C11">
+        <v>89</v>
+      </c>
+      <c r="D11">
+        <v>83</v>
+      </c>
+      <c r="E11">
+        <v>88</v>
+      </c>
+      <c r="F11">
+        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A19036</t>
+          <t>A26072</t>
         </is>
       </c>
       <c r="B12">
-        <v>63</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="C12">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>85</v>
+      </c>
+      <c r="E12">
+        <v>72</v>
+      </c>
+      <c r="F12">
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A19040</t>
+          <t>A26080</t>
         </is>
       </c>
       <c r="B13">
-        <v>58</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="C13">
+        <v>86</v>
+      </c>
+      <c r="D13">
+        <v>62</v>
+      </c>
+      <c r="E13">
+        <v>66</v>
+      </c>
+      <c r="F13">
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A19041</t>
+          <t>A26085</t>
         </is>
       </c>
       <c r="B14">
-        <v>76</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="C14">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>38</v>
+      </c>
+      <c r="F14">
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A19047</t>
+          <t>A26093</t>
         </is>
       </c>
       <c r="B15">
-        <v>49</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="C15">
+        <v>63</v>
+      </c>
+      <c r="D15">
+        <v>58</v>
+      </c>
+      <c r="E15">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A19052</t>
+          <t>A26101</t>
         </is>
       </c>
       <c r="B16">
-        <v>65</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="C16">
+        <v>68</v>
+      </c>
+      <c r="D16">
+        <v>67</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>70</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A19055</t>
+          <t>A26106</t>
         </is>
       </c>
       <c r="B17">
-        <v>61</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="C17">
+        <v>72</v>
+      </c>
+      <c r="D17">
+        <v>72</v>
+      </c>
+      <c r="E17">
+        <v>55</v>
+      </c>
+      <c r="F17">
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A19058</t>
+          <t>A26114</t>
         </is>
       </c>
       <c r="B18">
-        <v>69</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>60</v>
+      </c>
+      <c r="D18">
+        <v>43</v>
+      </c>
+      <c r="E18">
+        <v>36</v>
+      </c>
+      <c r="F18">
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A19060</t>
+          <t>A26122</t>
         </is>
       </c>
       <c r="B19">
-        <v>54</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>29</v>
+      </c>
+      <c r="E19">
+        <v>29</v>
+      </c>
+      <c r="F19">
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A19063</t>
+          <t>A26127</t>
         </is>
       </c>
       <c r="B20">
-        <v>72</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="C20">
+        <v>66</v>
+      </c>
+      <c r="D20">
+        <v>60</v>
+      </c>
+      <c r="E20">
+        <v>41</v>
+      </c>
+      <c r="F20">
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A19067</t>
+          <t>A26135</t>
         </is>
       </c>
       <c r="B21">
-        <v>60</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
+        <v>87</v>
+      </c>
+      <c r="C21">
+        <v>76</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>69</v>
+      </c>
+      <c r="F21">
+        <v>70</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>absent from the critique</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A19070</t>
+          <t>A26143</t>
         </is>
       </c>
       <c r="B22">
-        <v>57</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>85</v>
+      </c>
+      <c r="D22">
+        <v>89</v>
+      </c>
+      <c r="E22">
+        <v>77</v>
+      </c>
+      <c r="F22">
+        <v>88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A19074</t>
+          <t>A26148</t>
         </is>
       </c>
       <c r="B23">
-        <v>64</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="C23">
+        <v>63</v>
+      </c>
+      <c r="D23">
+        <v>58</v>
+      </c>
+      <c r="E23">
+        <v>56</v>
+      </c>
+      <c r="F23">
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A19077</t>
+          <t>A26156</t>
         </is>
       </c>
       <c r="B24">
-        <v>51</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>92</v>
+      </c>
+      <c r="C24">
+        <v>92</v>
+      </c>
+      <c r="D24">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>90</v>
+      </c>
+      <c r="F24">
+        <v>92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A19081</t>
+          <t>A26164</t>
         </is>
       </c>
       <c r="B25">
+        <v>83</v>
+      </c>
+      <c r="C25">
+        <v>72</v>
+      </c>
+      <c r="D25">
+        <v>80</v>
+      </c>
+      <c r="E25">
+        <v>79</v>
+      </c>
+      <c r="F25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A26169</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>68</v>
+      </c>
+      <c r="C26">
+        <v>55</v>
+      </c>
+      <c r="D26">
+        <v>55</v>
+      </c>
+      <c r="E26">
+        <v>53</v>
+      </c>
+      <c r="F26">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A26177</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>34</v>
+      </c>
+      <c r="C27">
+        <v>37</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <v>32</v>
+      </c>
+      <c r="F27">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A26185</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>92</v>
+      </c>
+      <c r="C28">
+        <v>90</v>
+      </c>
+      <c r="D28">
+        <v>91</v>
+      </c>
+      <c r="E28">
+        <v>86</v>
+      </c>
+      <c r="F28">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A26190</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>61</v>
+      </c>
+      <c r="C29">
+        <v>55</v>
+      </c>
+      <c r="D29">
+        <v>54</v>
+      </c>
+      <c r="E29">
+        <v>50</v>
+      </c>
+      <c r="F29">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A26198</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>85</v>
+      </c>
+      <c r="C30">
+        <v>78</v>
+      </c>
+      <c r="D30">
         <v>67</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E30">
+        <v>82</v>
+      </c>
+      <c r="F30">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A26206</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>39</v>
+      </c>
+      <c r="C31">
+        <v>59</v>
+      </c>
+      <c r="D31">
+        <v>43</v>
+      </c>
+      <c r="E31">
+        <v>41</v>
+      </c>
+      <c r="F31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A26211</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>26</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A26219</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>54</v>
+      </c>
+      <c r="D33">
+        <v>39</v>
+      </c>
+      <c r="E33">
+        <v>36</v>
+      </c>
+      <c r="F33">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A26227</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>66</v>
+      </c>
+      <c r="C34">
+        <v>66</v>
+      </c>
+      <c r="D34">
+        <v>71</v>
+      </c>
+      <c r="E34">
+        <v>43</v>
+      </c>
+      <c r="F34">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A26232</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>79</v>
+      </c>
+      <c r="C35">
+        <v>74</v>
+      </c>
+      <c r="D35">
+        <v>76</v>
+      </c>
+      <c r="E35">
+        <v>79</v>
+      </c>
+      <c r="F35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A26240</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>50</v>
+      </c>
+      <c r="C36">
+        <v>47</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A26248</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>78</v>
+      </c>
+      <c r="C37">
+        <v>81</v>
+      </c>
+      <c r="D37">
+        <v>77</v>
+      </c>
+      <c r="E37">
+        <v>63</v>
+      </c>
+      <c r="F37">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A26253</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>72</v>
+      </c>
+      <c r="C38">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>52</v>
+      </c>
+      <c r="E38">
+        <v>54</v>
+      </c>
+      <c r="F38">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A26261</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>72</v>
+      </c>
+      <c r="C39">
+        <v>79</v>
+      </c>
+      <c r="D39">
+        <v>80</v>
+      </c>
+      <c r="E39">
+        <v>61</v>
+      </c>
+      <c r="F39">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
